--- a/important_mails_2026-09-22.xlsx
+++ b/important_mails_2026-09-22.xlsx
@@ -1583,7 +1583,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1598,70 +1598,21 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
+          <t>Sun, 20 Sep 2026 15:02:02 +0000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+          <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Submit proof of insurance by January 18 to avoid listing
- deactivation</t>
+          <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
- Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
- Hello,
-Submit proof of commercial liability insurance by January 18, 2027, to continue selling categories with enhanced safety listing requirements on Amazon.com.
- To view your impacted products and categories, visit: Link to ASIN . Review the requirements and next steps below.
- Why is proof of insurance required?
- We are requiring proof of insurance because your listings in categories with enhanced safety require commercial liability insurance with a minimum coverage of $1 million per occurrence and in aggregate. Effective January 18, 2027, sellers with listings in these categories must maintain this coverage regardless of their gross proceeds. This requirement also applies to sellers who exceed USD $10,000 in gross proceeds in any month on Amazon.com, regardless of category.
- To learn more, go to Commercial Liability Insurance Requirements .
- How do I avoid listing deactivation?
- Complete the following steps by January 18, 2027:
-- Get insurance: Obtain a commercial general, excess, or umbrella liability insurance policy with minimum coverage of $1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 20 Sep 2026 15:02:02 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;
@@ -1676,39 +1627,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 16:29:22 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;
@@ -1723,39 +1674,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:36:30 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -1778,39 +1729,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:32:49 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Status materiałów niebezpiecznych (hazmat)
@@ -1833,39 +1784,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:02:50 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -1888,94 +1839,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Recover between 60-80%* from returns</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
- We handle the grading and reselling. You keep control of pricing and recover value.
- Your returns are worth more than you think.
- Every returned unit sitting idle is value left on the table. FBA Grade and Resell puts it back to work, we grade your returns and list them as Used for you, so you recover value without the extra manual effort.
- You stay in control. We do the heavy lifting.
- Recover value now
- Here's how it works:
- We grade every eligible unit — Returns are assessed and graded to the right condition, ready to sell as Used.
- You set your prices — Graded units enter the Used channel with you as the seller, at the recovery prices you set.
- You recover between 60 to 80%* — Reclaim value between 60–80%* from inventory that would otherwise go to waste, with none of the operational burden.
- Learn about Grade and Resell
- *Recovery rates are based on historical program performance data and represent gross recovery percentages before applicable fees. Individual recovery rates may vary.
- Report an issue with this email
- If you have any questions visit:
- Seller Central
- To change your email preferences visit:
- Notification Preferences
- We hope you found this message to be useful</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:29:10 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-01</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1996,39 +1892,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 03:52:36 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2052,39 +1948,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:54:38 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -2096,40 +1992,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 09:46:06 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -2148,40 +2044,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -2196,39 +2092,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -2256,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -2304,39 +2200,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -2359,39 +2255,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2407,39 +2303,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2455,39 +2351,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2503,39 +2399,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2551,39 +2447,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2599,39 +2495,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2647,39 +2543,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2695,39 +2591,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2747,39 +2643,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2795,39 +2691,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2843,39 +2739,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2895,39 +2791,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2943,39 +2839,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2991,39 +2887,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3039,39 +2935,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3091,39 +2987,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3139,39 +3035,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3191,39 +3087,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3239,39 +3135,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3296,39 +3192,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3341,39 +3237,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3389,39 +3285,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 30 Aug 2026 14:03:08 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3442,39 +3338,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:40:08 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3490,39 +3386,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 16:34:35 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0QNxXwzJgp)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3542,39 +3438,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 15:00:25 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3588,39 +3484,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 09:22:31 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3636,39 +3532,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 04:53:03 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3684,39 +3580,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 05:02:47 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3732,39 +3628,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 23:58:41 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0Bix9UfQE5)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3784,39 +3680,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 15:00:02 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3827,39 +3723,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 04:58:09 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3875,39 +3771,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 18:49:27 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (qO7a7il03F)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3927,39 +3823,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:33:42 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (aVWN9vWwFe)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3979,39 +3875,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 05:00:58 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4027,39 +3923,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4079,39 +3975,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4128,39 +4024,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4180,39 +4076,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>The Accelerate 2026 agenda got even better. See what's new.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
@@ -4230,39 +4126,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4282,39 +4178,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Discover sessions built for growing businesses, and save $200</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
@@ -4327,39 +4223,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4379,39 +4275,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4428,39 +4324,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4484,39 +4380,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -4532,39 +4428,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -4579,39 +4475,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4631,39 +4527,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4687,39 +4583,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1:1 expert access, new AI tools, and $200 off—register now</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
@@ -4735,40 +4631,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -4782,39 +4678,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4830,39 +4726,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4878,39 +4774,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -4924,39 +4820,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4976,39 +4872,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5025,39 +4921,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5077,39 +4973,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -5118,39 +5014,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 10:29:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends this Saturday—Register now</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-26/7z5f1dw/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5f1dz/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
@@ -5169,39 +5065,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:42:21 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5218,39 +5114,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:41:47 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5270,39 +5166,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 10:23:35 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Final Call: Early-bird pricing ends this Saturday, 8/29—Register now</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-25/7z5dp4h/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dp4l/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
@@ -5321,39 +5217,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 12:33:59 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Sellers called this one of the highlights of Accelerate</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-24/7z5dhr3/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dhr6/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
@@ -5369,39 +5265,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:24:04 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5425,39 +5321,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 12:38:26 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 29. Save $100 now</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596lw/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596lz/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
@@ -5473,40 +5369,89 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Submit proof of insurance by January 18 to avoid listing
+ deactivation</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
+ Hello,
+Submit proof of commercial liability insurance by January 18, 2027, to continue selling categories with enhanced safety listing requirements on Amazon.com.
+ To view your impacted products and categories, visit: Link to ASIN . Review the requirements and next steps below.
+ Why is proof of insurance required?
+ We are requiring proof of insurance because your listings in categories with enhanced safety require commercial liability insurance with a minimum coverage of $1 million per occurrence and in aggregate. Effective January 18, 2027, sellers with listings in these categories must maintain this coverage regardless of their gross proceeds. This requirement also applies to sellers who exceed USD $10,000 in gross proceeds in any month on Amazon.com, regardless of category.
+ To learn more, go to Commercial Liability Insurance Requirements .
+ How do I avoid listing deactivation?
+ Complete the following steps by January 18, 2027:
+- Get insurance: Obtain a commercial general, excess, or umbrella liability insurance policy with minimum coverage of $1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5525,39 +5470,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5579,39 +5524,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5629,39 +5574,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5679,39 +5624,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 08:06:37 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5729,39 +5674,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 17:08:09 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5779,39 +5724,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:07:40 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5829,39 +5774,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:40 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5880,39 +5825,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:40:10 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -5925,39 +5870,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:27 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5976,39 +5921,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:04 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6026,39 +5971,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:08:31 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6075,39 +6020,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:59:58 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6125,39 +6070,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:32 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6175,39 +6120,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6223,39 +6168,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6273,39 +6218,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6323,39 +6268,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 13:10:03 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6372,39 +6317,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:30:25 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6422,39 +6367,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:14:40 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6472,39 +6417,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 12:45:43 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6520,39 +6465,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 20:11:48 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6570,39 +6515,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 19:56:44 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6620,39 +6565,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:41:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -6661,39 +6606,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 16:03:11 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -6735,39 +6680,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 03:08:21 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6786,39 +6731,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:47:49 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -6828,39 +6773,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:15:11 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6879,39 +6824,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:11:05 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6930,39 +6875,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:08:01 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6980,39 +6925,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:28 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7031,39 +6976,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:08:21 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7082,39 +7027,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:34 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7133,39 +7078,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:29 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7184,39 +7129,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 14:07:29 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -7234,39 +7179,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:07:04 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7285,39 +7230,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 09:06:58 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7335,39 +7280,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 16:31:11 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -7402,40 +7347,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -7453,39 +7398,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 16:08:02 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7500,6 +7445,61 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
 -
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Recover between 60-80%* from returns</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We handle the grading and reselling. You keep control of pricing and recover value.
+ Your returns are worth more than you think.
+ Every returned unit sitting idle is value left on the table. FBA Grade and Resell puts it back to work, we grade your returns and list them as Used for you, so you recover value without the extra manual effort.
+ You stay in control. We do the heavy lifting.
+ Recover value now
+ Here's how it works:
+ We grade every eligible unit — Returns are assessed and graded to the right condition, ready to sell as Used.
+ You set your prices — Graded units enter the Used channel with you as the seller, at the recovery prices you set.
+ You recover between 60 to 80%* — Reclaim value between 60–80%* from inventory that would otherwise go to waste, with none of the operational burden.
+ Learn about Grade and Resell
+ *Recovery rates are based on historical program performance data and represent gross recovery percentages before applicable fees. Individual recovery rates may vary.
+ Report an issue with this email
+ If you have any questions visit:
+ Seller Central
+ To change your email preferences visit:
+ Notification Preferences
+ We hope you found this message to be useful</t>
         </is>
       </c>
     </row>
